--- a/files/template.xlsx
+++ b/files/template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\Certificate-verifier\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46F17CD9-C6C1-45CE-AE78-FEEE2135484F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62D8A5C1-73EE-41C9-8AFA-B5250069FCEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3000" yWindow="5280" windowWidth="17280" windowHeight="8880" xr2:uid="{E3C9BD67-6837-4041-A74B-69F2C158C764}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E3C9BD67-6837-4041-A74B-69F2C158C764}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,21 +36,18 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>control_number</t>
-  </si>
-  <si>
-    <t>teacher_email</t>
   </si>
   <si>
     <t>seminar_title</t>
   </si>
   <si>
-    <t>certificate_file</t>
+    <t>name</t>
   </si>
   <si>
-    <t>name</t>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -445,17 +442,15 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="E1" s="1"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D2" s="1"/>
